--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.34566958306239</v>
+        <v>1.518671307247639</v>
       </c>
       <c r="D2" t="n">
-        <v>24.22972098635751</v>
+        <v>3.937329660283095</v>
       </c>
       <c r="E2" t="n">
-        <v>5.936746367997967</v>
+        <v>0.9647212847996696</v>
       </c>
       <c r="F2" t="n">
-        <v>5.715721731769716</v>
+        <v>0.9288047814125789</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.70456650434219</v>
+        <v>1.901992056955607</v>
       </c>
       <c r="D3" t="n">
-        <v>18.67652269561976</v>
+        <v>3.034934938038211</v>
       </c>
       <c r="E3" t="n">
-        <v>5.936746367997967</v>
+        <v>0.9647212847996696</v>
       </c>
       <c r="F3" t="n">
-        <v>5.715721731769716</v>
+        <v>0.9288047814125789</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.95206507251026</v>
+        <v>3.729710574282918</v>
       </c>
       <c r="D4" t="n">
-        <v>10.32279710738714</v>
+        <v>1.67745452995041</v>
       </c>
       <c r="E4" t="n">
-        <v>5.936746367997967</v>
+        <v>0.9647212847996696</v>
       </c>
       <c r="F4" t="n">
-        <v>5.715721731769716</v>
+        <v>0.9288047814125789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
